--- a/packages/payday-super-checker/workbooks/payday-super-checker.xlsx
+++ b/packages/payday-super-checker/workbooks/payday-super-checker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15"/>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6A45B7C-8484-47A8-8850-EA02003EFAC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D803C876-E965-4529-8BED-7102C166DD1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
     <t>Overall status</t>
   </si>
   <si>
-    <t>payday-super-checker workbook, engine 0.1.3. Macro-free. Not advice; see DISCLAIMER.md in the repository.</t>
+    <t>payday-super-checker workbook, engine 0.1.4. Macro-free. Not advice; see DISCLAIMER.md in the repository.</t>
   </si>
   <si>
     <t>employee_id</t>
@@ -691,7 +691,7 @@
     <t>Workbook engine version</t>
   </si>
   <si>
-    <t>0.1.3</t>
+    <t>0.1.4</t>
   </si>
   <si>
     <t>Desktop Excel build used to calculate cached values</t>
@@ -733,7 +733,7 @@
     <t>Experimental review aid. Not a compliance determination, not an ATO assessment, and not tax, legal or financial advice.</t>
   </si>
   <si>
-    <t>Excel 16.0 build 20326</t>
+    <t>Excel 16.0 build 20430</t>
   </si>
 </sst>
 </file>
